--- a/SGC-CKN/Excel/989d0697-4753-48b9-8306-a7b1acad8633_Lô_CT-02_P_I-126_D800_24-01-2026.xlsx
+++ b/SGC-CKN/Excel/989d0697-4753-48b9-8306-a7b1acad8633_Lô_CT-02_P_I-126_D800_24-01-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P.I-126</t>
+    <t>P7-126</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>09:00 23/01/2026</t>
+    <t>09:00 23/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>04:17 24/01/2026</t>
+    <t>04:17 24/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">09:00
-23/01/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:15
-23/01/2026</t>
+23/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:16
+23/03/2026</t>
   </si>
   <si>
     <t/>
@@ -116,11 +116,11 @@
   </si>
   <si>
     <t xml:space="preserve">09:17
-23/01/2026</t>
+23/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">09:23
-23/01/2026</t>
+23/03/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -130,11 +130,11 @@
   </si>
   <si>
     <t xml:space="preserve">09:24
-23/01/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:50
-23/01/2026</t>
+23/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:30
+23/03/2026</t>
   </si>
   <si>
     <t>Máy hỏng từ 11:20 đến 22:08</t>
@@ -147,11 +147,11 @@
   </si>
   <si>
     <t xml:space="preserve">22:09
-23/01/2026</t>
+23/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">22:55
-23/01/2026</t>
+23/03/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -160,12 +160,12 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">22:58
-23/01/2026</t>
+    <t xml:space="preserve">22:56
+23/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">23:41
-23/01/2026</t>
+23/03/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -175,7 +175,7 @@
   </si>
   <si>
     <t xml:space="preserve">01:28
-24/01/2026</t>
+24/03/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -185,11 +185,11 @@
   </si>
   <si>
     <t xml:space="preserve">01:29
-24/01/2026</t>
+24/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">01:51
-24/01/2026</t>
+24/03/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -199,7 +199,7 @@
   </si>
   <si>
     <t xml:space="preserve">02:08
-24/01/2026</t>
+24/03/2026</t>
   </si>
   <si>
     <t>9</t>
@@ -209,11 +209,11 @@
   </si>
   <si>
     <t xml:space="preserve">02:09
-24/01/2026</t>
+24/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">03:45
-24/01/2026</t>
+24/03/2026</t>
   </si>
   <si>
     <t>10</t>
@@ -223,11 +223,11 @@
   </si>
   <si>
     <t xml:space="preserve">03:46
-24/01/2026</t>
+24/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">04:17
-24/01/2026</t>
+24/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -1234,19 +1234,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-5.6</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-7.01</v>
       </c>
       <c r="H11" s="5">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="I11" s="5">
-        <v>1.41</v>
+        <v>7.01</v>
       </c>
       <c r="J11" s="8">
-        <v>5.64</v>
+        <v>26.29</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1272,16 +1272,16 @@
         <v>-7.01</v>
       </c>
       <c r="G12" s="9">
-        <v>-9.46</v>
+        <v>-9.16</v>
       </c>
       <c r="H12" s="9">
         <v>0.1</v>
       </c>
       <c r="I12" s="9">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="J12" s="8">
-        <v>24.5</v>
+        <v>21.5</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1304,19 +1304,19 @@
         <v>38</v>
       </c>
       <c r="F13" s="12">
-        <v>-9.46</v>
+        <v>-9.16</v>
       </c>
       <c r="G13" s="12">
         <v>-17.36</v>
       </c>
       <c r="H13" s="12">
-        <v>0.43</v>
+        <v>0.1</v>
       </c>
       <c r="I13" s="12">
-        <v>7.9</v>
+        <v>8.2</v>
       </c>
       <c r="J13" s="8">
-        <v>18.23</v>
+        <v>82</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>39</v>
@@ -1342,16 +1342,16 @@
         <v>-17.36</v>
       </c>
       <c r="G14" s="15">
-        <v>-21.6</v>
+        <v>-21.36</v>
       </c>
       <c r="H14" s="15">
         <v>0.77</v>
       </c>
       <c r="I14" s="15">
-        <v>4.24</v>
+        <v>4</v>
       </c>
       <c r="J14" s="8">
-        <v>5.53</v>
+        <v>5.22</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>30</v>
@@ -1374,19 +1374,19 @@
         <v>47</v>
       </c>
       <c r="F15" s="18">
-        <v>-21.6</v>
+        <v>-21.36</v>
       </c>
       <c r="G15" s="18">
         <v>-25.7</v>
       </c>
       <c r="H15" s="18">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="I15" s="18">
-        <v>4.1</v>
+        <v>4.34</v>
       </c>
       <c r="J15" s="8">
-        <v>5.72</v>
+        <v>5.79</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>30</v>
@@ -1447,16 +1447,16 @@
         <v>-35.6</v>
       </c>
       <c r="G17" s="24">
-        <v>-37.6</v>
+        <v>-37.67</v>
       </c>
       <c r="H17" s="24">
         <v>0.37</v>
       </c>
       <c r="I17" s="24">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="J17" s="8">
-        <v>5.45</v>
+        <v>5.65</v>
       </c>
       <c r="K17" s="25" t="s">
         <v>30</v>
@@ -1479,7 +1479,7 @@
         <v>57</v>
       </c>
       <c r="F18" s="27">
-        <v>-37.6</v>
+        <v>-37.67</v>
       </c>
       <c r="G18" s="27">
         <v>-39.2</v>
@@ -1488,10 +1488,10 @@
         <v>0.28</v>
       </c>
       <c r="I18" s="27">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="J18" s="8">
-        <v>5.65</v>
+        <v>5.4</v>
       </c>
       <c r="K18" s="28" t="s">
         <v>30</v>
@@ -1552,16 +1552,16 @@
         <v>-43.85</v>
       </c>
       <c r="G20" s="34">
-        <v>-45.3</v>
+        <v>-45</v>
       </c>
       <c r="H20" s="34">
         <v>0.52</v>
       </c>
       <c r="I20" s="34">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="J20" s="33">
-        <v>2.81</v>
+        <v>2.23</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
@@ -1716,19 +1716,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-5.6</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-7.01</v>
       </c>
       <c r="G2" s="5">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="H2" s="5">
-        <v>1.41</v>
+        <v>7.01</v>
       </c>
       <c r="I2" s="8">
-        <v>5.64</v>
+        <v>26.29</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1748,16 +1748,16 @@
         <v>-7.01</v>
       </c>
       <c r="F3" s="9">
-        <v>-9.46</v>
+        <v>-9.16</v>
       </c>
       <c r="G3" s="9">
         <v>0.1</v>
       </c>
       <c r="H3" s="9">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="I3" s="8">
-        <v>24.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1774,19 +1774,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="12">
-        <v>-9.46</v>
+        <v>-9.16</v>
       </c>
       <c r="F4" s="12">
         <v>-17.36</v>
       </c>
       <c r="G4" s="12">
-        <v>0.43</v>
+        <v>0.1</v>
       </c>
       <c r="H4" s="12">
-        <v>7.9</v>
+        <v>8.2</v>
       </c>
       <c r="I4" s="8">
-        <v>18.23</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1806,16 +1806,16 @@
         <v>-17.36</v>
       </c>
       <c r="F5" s="15">
-        <v>-21.6</v>
+        <v>-21.36</v>
       </c>
       <c r="G5" s="15">
         <v>0.77</v>
       </c>
       <c r="H5" s="15">
-        <v>4.24</v>
+        <v>4</v>
       </c>
       <c r="I5" s="8">
-        <v>5.53</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1832,19 +1832,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="18">
-        <v>-21.6</v>
+        <v>-21.36</v>
       </c>
       <c r="F6" s="18">
         <v>-25.7</v>
       </c>
       <c r="G6" s="18">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="H6" s="18">
-        <v>4.1</v>
+        <v>4.34</v>
       </c>
       <c r="I6" s="8">
-        <v>5.72</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1893,16 +1893,16 @@
         <v>-35.6</v>
       </c>
       <c r="F8" s="24">
-        <v>-37.6</v>
+        <v>-37.67</v>
       </c>
       <c r="G8" s="24">
         <v>0.37</v>
       </c>
       <c r="H8" s="24">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="I8" s="8">
-        <v>5.45</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1919,7 +1919,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="27">
-        <v>-37.6</v>
+        <v>-37.67</v>
       </c>
       <c r="F9" s="27">
         <v>-39.2</v>
@@ -1928,10 +1928,10 @@
         <v>0.28</v>
       </c>
       <c r="H9" s="27">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="I9" s="8">
-        <v>5.65</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1980,16 +1980,16 @@
         <v>-43.85</v>
       </c>
       <c r="F11" s="34">
-        <v>-45.3</v>
+        <v>-45</v>
       </c>
       <c r="G11" s="34">
         <v>0.52</v>
       </c>
       <c r="H11" s="34">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="I11" s="33">
-        <v>2.81</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2006,19 +2006,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-5.6</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
-        <v>-45.3</v>
+        <v>-45</v>
       </c>
       <c r="G12" s="39">
-        <v>6.82</v>
+        <v>6.53</v>
       </c>
       <c r="H12" s="39">
-        <v>39.7</v>
+        <v>45</v>
       </c>
       <c r="I12" s="39">
-        <v>5.82</v>
+        <v>6.89</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/989d0697-4753-48b9-8306-a7b1acad8633_Lô_CT-02_P_I-126_D800_24-01-2026.xlsx
+++ b/SGC-CKN/Excel/989d0697-4753-48b9-8306-a7b1acad8633_Lô_CT-02_P_I-126_D800_24-01-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
   <si>
     <t>Dự án</t>
   </si>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">09:00
@@ -112,7 +112,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét pha xám ghi, xám nâu TT dẻo</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">09:17
@@ -143,7 +143,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">22:09
@@ -157,7 +157,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">22:56
@@ -171,7 +171,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">01:28
@@ -181,7 +181,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">01:29
@@ -195,7 +195,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>TK-16.1. Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">02:08
@@ -205,9 +205,6 @@
     <t>9</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">02:09
 24/03/2026</t>
   </si>
@@ -219,7 +216,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
+    <t>Cuội đa màu sắc, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">03:46
@@ -1505,13 +1502,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="E19" s="32" t="s">
         <v>60</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>61</v>
       </c>
       <c r="F19" s="30">
         <v>-39.2</v>
@@ -1534,19 +1531,19 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="E20" s="36" t="s">
         <v>64</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>65</v>
       </c>
       <c r="F20" s="34">
         <v>-43.85</v>
@@ -1569,7 +1566,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1675,31 +1672,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1942,7 +1939,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D10" s="30">
         <v>1</v>
@@ -1971,7 +1968,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1994,7 +1991,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
